--- a/sample-products.xlsx
+++ b/sample-products.xlsx
@@ -1,41 +1,146 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fashion-store\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_37CB603F92387D6A20610226E0508BFBA02C0C94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>sizes</t>
+  </si>
+  <si>
+    <t>badge</t>
+  </si>
+  <si>
+    <t>emoji</t>
+  </si>
+  <si>
+    <t>bg</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>Draped Satin Blouse</t>
+  </si>
+  <si>
+    <t>Maison Elite</t>
+  </si>
+  <si>
+    <t>Women</t>
+  </si>
+  <si>
+    <t>XS,S,M,L</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>👗</t>
+  </si>
+  <si>
+    <t>#F5EEE6,#EDE4D8</t>
+  </si>
+  <si>
+    <t>Elegant satin blouse for formal and casual styling.</t>
+  </si>
+  <si>
+    <t>https://example.com/images/blouse-101.jpg</t>
+  </si>
+  <si>
+    <t>Tailored Wool Blazer</t>
+  </si>
+  <si>
+    <t>LAtelier</t>
+  </si>
+  <si>
+    <t>Men</t>
+  </si>
+  <si>
+    <t>S,M,L,XL</t>
+  </si>
+  <si>
+    <t>Best Seller</t>
+  </si>
+  <si>
+    <t>🧥</t>
+  </si>
+  <si>
+    <t>#E9F4FF,#D7E8FF</t>
+  </si>
+  <si>
+    <t>Structured wool blazer with modern fit.</t>
+  </si>
+  <si>
+    <t>https://example.com/images/blazer-102.jpg</t>
+  </si>
+  <si>
+    <t>Mini Crossbody Bag</t>
+  </si>
+  <si>
+    <t>Urban Loom</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Free Size</t>
+  </si>
+  <si>
+    <t>Limited</t>
+  </si>
+  <si>
+    <t>👜</t>
+  </si>
+  <si>
+    <t>#F7EFE3,#EADBC8</t>
+  </si>
+  <si>
+    <t>Compact everyday crossbody with premium hardware.</t>
+  </si>
+  <si>
+    <t>https://example.com/images/bag-103.jpg</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +170,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,152 +509,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>brand</v>
-      </c>
-      <c r="D1" t="str">
-        <v>price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>category</v>
-      </c>
-      <c r="F1" t="str">
-        <v>sizes</v>
-      </c>
-      <c r="G1" t="str">
-        <v>badge</v>
-      </c>
-      <c r="H1" t="str">
-        <v>emoji</v>
-      </c>
-      <c r="I1" t="str">
-        <v>bg</v>
-      </c>
-      <c r="J1" t="str">
-        <v>desc</v>
-      </c>
-      <c r="K1" t="str">
-        <v>image</v>
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Draped Satin Blouse</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Maison Elite</v>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
       <c r="D2">
         <v>245</v>
       </c>
-      <c r="E2" t="str">
-        <v>Women</v>
-      </c>
-      <c r="F2" t="str">
-        <v>XS,S,M,L</v>
-      </c>
-      <c r="G2" t="str">
-        <v>New</v>
-      </c>
-      <c r="H2" t="str">
-        <v>👗</v>
-      </c>
-      <c r="I2" t="str">
-        <v>#F5EEE6,#EDE4D8</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Elegant satin blouse for formal and casual styling.</v>
-      </c>
-      <c r="K2" t="str">
-        <v>https://example.com/images/blouse-101.jpg</v>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Tailored Wool Blazer</v>
-      </c>
-      <c r="C3" t="str">
-        <v>LAtelier</v>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
       <c r="D3">
         <v>480</v>
       </c>
-      <c r="E3" t="str">
-        <v>Men</v>
-      </c>
-      <c r="F3" t="str">
-        <v>S,M,L,XL</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Best Seller</v>
-      </c>
-      <c r="H3" t="str">
-        <v>🧥</v>
-      </c>
-      <c r="I3" t="str">
-        <v>#E9F4FF,#D7E8FF</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Structured wool blazer with modern fit.</v>
-      </c>
-      <c r="K3" t="str">
-        <v>https://example.com/images/blazer-102.jpg</v>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Mini Crossbody Bag</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Urban Loom</v>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
       </c>
       <c r="D4">
         <v>130</v>
       </c>
-      <c r="E4" t="str">
-        <v>Accessories</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Free Size</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Limited</v>
-      </c>
-      <c r="H4" t="str">
-        <v>👜</v>
-      </c>
-      <c r="I4" t="str">
-        <v>#F7EFE3,#EADBC8</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Compact everyday crossbody with premium hardware.</v>
-      </c>
-      <c r="K4" t="str">
-        <v>https://example.com/images/bag-103.jpg</v>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError sqref="A1:K4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>